--- a/Agentes/Maria/Sistemas de RH/Relatórios/2026-08/Radar Diário do Ponto - 2026-08-14.xlsx
+++ b/Agentes/Maria/Sistemas de RH/Relatórios/2026-08/Radar Diário do Ponto - 2026-08-14.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15/08/2026 11:03:31 BRT</t>
+          <t>15/08/2026 11:04:12 BRT</t>
         </is>
       </c>
     </row>
